--- a/data/trans_dic/MCS12_SP_R3-Provincia-trans_dic.xlsx
+++ b/data/trans_dic/MCS12_SP_R3-Provincia-trans_dic.xlsx
@@ -527,7 +527,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Población en el primer cuartil de la puntuación del componente de salud mental (SF12)</t>
+          <t>Población en el primer cuartil (48.388) de la puntuación del componente de salud mental (SF12) (tasa de respuesta: 99,81%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -717,62 +717,62 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>13,31; 22,51</t>
+          <t>13,3; 23,22</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>27,69; 38,46</t>
+          <t>27,12; 38,3</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>25,88; 37,11</t>
+          <t>26,3; 37,14</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>4,3; 9,66</t>
+          <t>4,26; 10,09</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>20,7; 31,48</t>
+          <t>20,2; 31,43</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>46,78; 58,95</t>
+          <t>46,58; 59,17</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>38,11; 49,32</t>
+          <t>37,9; 49,64</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
         <is>
-          <t>5,01; 9,8</t>
+          <t>5,18; 9,79</t>
         </is>
       </c>
       <c r="K5" s="2" t="inlineStr">
         <is>
-          <t>18,32; 25,35</t>
+          <t>17,75; 25,44</t>
         </is>
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>38,53; 46,8</t>
+          <t>38,62; 46,9</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>33,49; 41,68</t>
+          <t>33,07; 41,2</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
         <is>
-          <t>5,29; 9,02</t>
+          <t>5,27; 8,87</t>
         </is>
       </c>
     </row>
@@ -857,62 +857,62 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>22,76; 31,11</t>
+          <t>22,63; 30,84</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>12,37; 19,2</t>
+          <t>11,89; 18,64</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>6,26; 11,33</t>
+          <t>6,33; 11,11</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>12,35; 19,64</t>
+          <t>12,02; 19,45</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>36,71; 45,2</t>
+          <t>36,6; 45,42</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>22,15; 29,71</t>
+          <t>21,71; 29,47</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>12,35; 18,79</t>
+          <t>12,54; 19,12</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
         <is>
-          <t>21,14; 28,14</t>
+          <t>21,2; 27,95</t>
         </is>
       </c>
       <c r="K7" s="2" t="inlineStr">
         <is>
-          <t>30,41; 36,73</t>
+          <t>30,95; 36,91</t>
         </is>
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>17,95; 23,31</t>
+          <t>18,0; 23,35</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>10,14; 14,32</t>
+          <t>10,03; 14,09</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
         <is>
-          <t>17,57; 22,91</t>
+          <t>17,36; 22,51</t>
         </is>
       </c>
     </row>
@@ -997,62 +997,62 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>2,02; 6,56</t>
+          <t>1,92; 6,58</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>11,34; 20,05</t>
+          <t>11,2; 19,11</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>7,32; 13,71</t>
+          <t>7,0; 13,46</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>9,62; 16,67</t>
+          <t>9,96; 16,95</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>7,25; 13,89</t>
+          <t>7,14; 14,2</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>19,27; 28,52</t>
+          <t>19,17; 28,19</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>11,31; 19,14</t>
+          <t>11,39; 18,73</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>16,55; 23,17</t>
+          <t>16,41; 23,35</t>
         </is>
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>5,23; 9,22</t>
+          <t>5,22; 9,11</t>
         </is>
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>16,46; 22,68</t>
+          <t>16,39; 22,26</t>
         </is>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>10,14; 15,23</t>
+          <t>10,07; 14,89</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
         <is>
-          <t>14,2; 19,3</t>
+          <t>14,24; 19,27</t>
         </is>
       </c>
     </row>
@@ -1137,62 +1137,62 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>6,63; 13,47</t>
+          <t>6,87; 13,4</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>17,99; 27,25</t>
+          <t>18,3; 27,13</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>15,66; 23,41</t>
+          <t>15,64; 23,48</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>9,03; 17,53</t>
+          <t>8,81; 16,9</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>13,0; 20,6</t>
+          <t>12,88; 20,29</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>37,37; 47,55</t>
+          <t>37,6; 47,26</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>27,5; 37,43</t>
+          <t>27,37; 37,68</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
         <is>
-          <t>10,76; 22,96</t>
+          <t>10,44; 22,56</t>
         </is>
       </c>
       <c r="K11" s="2" t="inlineStr">
         <is>
-          <t>10,8; 15,93</t>
+          <t>10,76; 15,74</t>
         </is>
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>29,22; 36,0</t>
+          <t>28,94; 35,79</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>22,46; 29,45</t>
+          <t>22,65; 29,53</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
         <is>
-          <t>11,23; 18,79</t>
+          <t>11,1; 18,74</t>
         </is>
       </c>
     </row>
@@ -1277,62 +1277,62 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t>24,79; 37,08</t>
+          <t>24,52; 37,44</t>
         </is>
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>8,96; 18,19</t>
+          <t>9,01; 18,41</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>34,47; 47,91</t>
+          <t>34,23; 48,03</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>42,16; 54,65</t>
+          <t>41,87; 55,5</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
         <is>
-          <t>31,76; 44,74</t>
+          <t>32,2; 45,33</t>
         </is>
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>25,7; 38,24</t>
+          <t>25,29; 38,14</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>43,74; 57,72</t>
+          <t>44,01; 56,84</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
         <is>
-          <t>55,13; 64,76</t>
+          <t>54,94; 64,72</t>
         </is>
       </c>
       <c r="K13" s="2" t="inlineStr">
         <is>
-          <t>29,81; 38,79</t>
+          <t>29,58; 39,06</t>
         </is>
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>18,68; 26,76</t>
+          <t>18,43; 26,51</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>41,86; 50,75</t>
+          <t>41,69; 50,74</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
         <is>
-          <t>50,75; 58,74</t>
+          <t>50,83; 59,05</t>
         </is>
       </c>
     </row>
@@ -1417,62 +1417,62 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>3,11; 8,6</t>
+          <t>2,88; 8,35</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>12,31; 21,47</t>
+          <t>12,15; 21,23</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>8,45; 16,65</t>
+          <t>8,59; 16,67</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>12,83; 20,67</t>
+          <t>12,54; 20,44</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
         <is>
-          <t>10,99; 20,05</t>
+          <t>11,31; 19,85</t>
         </is>
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
-          <t>20,72; 31,22</t>
+          <t>21,01; 31,48</t>
         </is>
       </c>
       <c r="I15" s="2" t="inlineStr">
         <is>
-          <t>18,36; 28,22</t>
+          <t>18,7; 29,26</t>
         </is>
       </c>
       <c r="J15" s="2" t="inlineStr">
         <is>
-          <t>16,54; 24,07</t>
+          <t>16,58; 23,62</t>
         </is>
       </c>
       <c r="K15" s="2" t="inlineStr">
         <is>
-          <t>7,52; 12,72</t>
+          <t>7,46; 12,79</t>
         </is>
       </c>
       <c r="L15" s="2" t="inlineStr">
         <is>
-          <t>17,51; 24,52</t>
+          <t>17,73; 24,82</t>
         </is>
       </c>
       <c r="M15" s="2" t="inlineStr">
         <is>
-          <t>14,49; 21,43</t>
+          <t>14,54; 21,57</t>
         </is>
       </c>
       <c r="N15" s="2" t="inlineStr">
         <is>
-          <t>15,43; 20,74</t>
+          <t>15,47; 20,61</t>
         </is>
       </c>
     </row>
@@ -1557,62 +1557,62 @@
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
-          <t>11,39; 17,24</t>
+          <t>11,39; 17,23</t>
         </is>
       </c>
       <c r="D17" s="2" t="inlineStr">
         <is>
-          <t>16,11; 22,56</t>
+          <t>16,1; 22,17</t>
         </is>
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>17,39; 24,12</t>
+          <t>17,23; 24,11</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>23,27; 32,16</t>
+          <t>22,64; 31,76</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
         <is>
-          <t>16,99; 23,31</t>
+          <t>17,35; 23,64</t>
         </is>
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>20,37; 27,34</t>
+          <t>20,71; 27,24</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>26,4; 33,72</t>
+          <t>26,31; 33,69</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
         <is>
-          <t>35,48; 81,13</t>
+          <t>35,55; 76,54</t>
         </is>
       </c>
       <c r="K17" s="2" t="inlineStr">
         <is>
-          <t>15,2; 19,27</t>
+          <t>15,31; 19,51</t>
         </is>
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>19,08; 23,85</t>
+          <t>19,17; 23,83</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>23,01; 28,02</t>
+          <t>23,06; 27,98</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
         <is>
-          <t>31,06; 65,43</t>
+          <t>30,84; 65,51</t>
         </is>
       </c>
     </row>
@@ -1697,62 +1697,62 @@
       </c>
       <c r="C19" s="2" t="inlineStr">
         <is>
-          <t>26,33; 32,85</t>
+          <t>26,49; 33,16</t>
         </is>
       </c>
       <c r="D19" s="2" t="inlineStr">
         <is>
-          <t>29,85; 36,89</t>
+          <t>29,8; 37,2</t>
         </is>
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>16,17; 21,82</t>
+          <t>16,15; 22,07</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>7,42; 23,47</t>
+          <t>7,49; 23,67</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
         <is>
-          <t>32,43; 39,46</t>
+          <t>32,38; 39,28</t>
         </is>
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>35,61; 42,63</t>
+          <t>35,48; 42,65</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>19,62; 25,72</t>
+          <t>19,72; 25,78</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
         <is>
-          <t>27,49; 33,07</t>
+          <t>27,44; 33,57</t>
         </is>
       </c>
       <c r="K19" s="2" t="inlineStr">
         <is>
-          <t>30,4; 35,38</t>
+          <t>30,55; 35,25</t>
         </is>
       </c>
       <c r="L19" s="2" t="inlineStr">
         <is>
-          <t>34,21; 39,01</t>
+          <t>33,71; 38,84</t>
         </is>
       </c>
       <c r="M19" s="2" t="inlineStr">
         <is>
-          <t>18,93; 23,24</t>
+          <t>18,85; 23,06</t>
         </is>
       </c>
       <c r="N19" s="2" t="inlineStr">
         <is>
-          <t>13,73; 27,34</t>
+          <t>13,3; 27,06</t>
         </is>
       </c>
     </row>
@@ -1837,62 +1837,62 @@
       </c>
       <c r="C21" s="2" t="inlineStr">
         <is>
-          <t>17,32; 20,03</t>
+          <t>17,4; 20,22</t>
         </is>
       </c>
       <c r="D21" s="2" t="inlineStr">
         <is>
-          <t>20,83; 23,76</t>
+          <t>20,79; 23,79</t>
         </is>
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>17,49; 20,2</t>
+          <t>17,6; 20,27</t>
         </is>
       </c>
       <c r="F21" s="2" t="inlineStr">
         <is>
-          <t>14,1; 20,31</t>
+          <t>14,57; 20,4</t>
         </is>
       </c>
       <c r="G21" s="2" t="inlineStr">
         <is>
-          <t>24,9; 28,14</t>
+          <t>25,04; 28,05</t>
         </is>
       </c>
       <c r="H21" s="2" t="inlineStr">
         <is>
-          <t>31,08; 34,52</t>
+          <t>30,98; 34,2</t>
         </is>
       </c>
       <c r="I21" s="2" t="inlineStr">
         <is>
-          <t>25,34; 28,3</t>
+          <t>25,33; 28,42</t>
         </is>
       </c>
       <c r="J21" s="2" t="inlineStr">
         <is>
-          <t>26,16; 43,29</t>
+          <t>26,19; 43,77</t>
         </is>
       </c>
       <c r="K21" s="2" t="inlineStr">
         <is>
-          <t>21,7; 23,73</t>
+          <t>21,74; 23,58</t>
         </is>
       </c>
       <c r="L21" s="2" t="inlineStr">
         <is>
-          <t>26,45; 28,57</t>
+          <t>26,49; 28,69</t>
         </is>
       </c>
       <c r="M21" s="2" t="inlineStr">
         <is>
-          <t>21,91; 23,92</t>
+          <t>21,93; 23,97</t>
         </is>
       </c>
       <c r="N21" s="2" t="inlineStr">
         <is>
-          <t>21,89; 32,04</t>
+          <t>21,81; 32,8</t>
         </is>
       </c>
     </row>
@@ -1951,7 +1951,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Población en el primer cuartil de la puntuación del componente de salud mental (SF12)</t>
+          <t>Población en el primer cuartil (48.388) de la puntuación del componente de salud mental (SF12) (tasa de respuesta: 99,81%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -2209,62 +2209,62 @@
       </c>
       <c r="C6" s="2" t="inlineStr">
         <is>
-          <t>36346; 61454</t>
+          <t>36303; 63398</t>
         </is>
       </c>
       <c r="D6" s="2" t="inlineStr">
         <is>
-          <t>81609; 113356</t>
+          <t>79934; 112898</t>
         </is>
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>76015; 109012</t>
+          <t>77257; 109096</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>13394; 30090</t>
+          <t>13262; 31424</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
         <is>
-          <t>53982; 82108</t>
+          <t>52683; 81990</t>
         </is>
       </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t>134363; 169324</t>
+          <t>133790; 169955</t>
         </is>
       </c>
       <c r="I6" s="2" t="inlineStr">
         <is>
-          <t>110030; 142401</t>
+          <t>109421; 143319</t>
         </is>
       </c>
       <c r="J6" s="2" t="inlineStr">
         <is>
-          <t>14506; 28378</t>
+          <t>14996; 28351</t>
         </is>
       </c>
       <c r="K6" s="2" t="inlineStr">
         <is>
-          <t>97806; 135334</t>
+          <t>94771; 135794</t>
         </is>
       </c>
       <c r="L6" s="2" t="inlineStr">
         <is>
-          <t>224215; 272366</t>
+          <t>224754; 272928</t>
         </is>
       </c>
       <c r="M6" s="2" t="inlineStr">
         <is>
-          <t>195057; 242773</t>
+          <t>192628; 239974</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
         <is>
-          <t>31826; 54211</t>
+          <t>31695; 53301</t>
         </is>
       </c>
     </row>
@@ -2417,62 +2417,62 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>112209; 153398</t>
+          <t>111561; 152040</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>62557; 97084</t>
+          <t>60085; 94249</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>31472; 56934</t>
+          <t>31819; 55838</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>63912; 101637</t>
+          <t>62230; 100646</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>184984; 227786</t>
+          <t>184458; 228889</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>116027; 155628</t>
+          <t>113731; 154365</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>64617; 98291</t>
+          <t>65582; 100000</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>108573; 144533</t>
+          <t>108890; 143553</t>
         </is>
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>303154; 366230</t>
+          <t>308599; 367989</t>
         </is>
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>184763; 239879</t>
+          <t>185250; 240382</t>
         </is>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>104015; 146895</t>
+          <t>102859; 144465</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
         <is>
-          <t>181174; 236185</t>
+          <t>178970; 232149</t>
         </is>
       </c>
     </row>
@@ -2625,62 +2625,62 @@
       </c>
       <c r="C12" s="2" t="inlineStr">
         <is>
-          <t>6437; 20914</t>
+          <t>6113; 20969</t>
         </is>
       </c>
       <c r="D12" s="2" t="inlineStr">
         <is>
-          <t>36744; 64970</t>
+          <t>36289; 61924</t>
         </is>
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>23317; 43668</t>
+          <t>22299; 42895</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>30212; 52368</t>
+          <t>31287; 53242</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
         <is>
-          <t>24330; 46596</t>
+          <t>23939; 47641</t>
         </is>
       </c>
       <c r="H12" s="2" t="inlineStr">
         <is>
-          <t>65729; 97274</t>
+          <t>65361; 96149</t>
         </is>
       </c>
       <c r="I12" s="2" t="inlineStr">
         <is>
-          <t>38033; 64371</t>
+          <t>38311; 63005</t>
         </is>
       </c>
       <c r="J12" s="2" t="inlineStr">
         <is>
-          <t>56934; 79717</t>
+          <t>56455; 80364</t>
         </is>
       </c>
       <c r="K12" s="2" t="inlineStr">
         <is>
-          <t>34206; 60317</t>
+          <t>34123; 59618</t>
         </is>
       </c>
       <c r="L12" s="2" t="inlineStr">
         <is>
-          <t>109460; 150829</t>
+          <t>109011; 148034</t>
         </is>
       </c>
       <c r="M12" s="2" t="inlineStr">
         <is>
-          <t>66432; 99763</t>
+          <t>65950; 97523</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
         <is>
-          <t>93467; 127053</t>
+          <t>93694; 126847</t>
         </is>
       </c>
     </row>
@@ -2833,62 +2833,62 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>23789; 48305</t>
+          <t>24631; 48044</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>67274; 101899</t>
+          <t>68443; 101456</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>57949; 86590</t>
+          <t>57857; 86883</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>27657; 53668</t>
+          <t>26987; 51757</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
         <is>
-          <t>48296; 76528</t>
+          <t>47843; 75369</t>
         </is>
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
-          <t>145341; 184947</t>
+          <t>146253; 183828</t>
         </is>
       </c>
       <c r="I15" s="2" t="inlineStr">
         <is>
-          <t>106506; 144957</t>
+          <t>105987; 145941</t>
         </is>
       </c>
       <c r="J15" s="2" t="inlineStr">
         <is>
-          <t>50611; 108008</t>
+          <t>49130; 106157</t>
         </is>
       </c>
       <c r="K15" s="2" t="inlineStr">
         <is>
-          <t>78821; 116294</t>
+          <t>78551; 114897</t>
         </is>
       </c>
       <c r="L15" s="2" t="inlineStr">
         <is>
-          <t>222947; 274633</t>
+          <t>220787; 273079</t>
         </is>
       </c>
       <c r="M15" s="2" t="inlineStr">
         <is>
-          <t>170083; 223017</t>
+          <t>171482; 223621</t>
         </is>
       </c>
       <c r="N15" s="2" t="inlineStr">
         <is>
-          <t>87250; 145927</t>
+          <t>86228; 145521</t>
         </is>
       </c>
     </row>
@@ -3041,62 +3041,62 @@
       </c>
       <c r="C18" s="2" t="inlineStr">
         <is>
-          <t>50407; 75394</t>
+          <t>49847; 76126</t>
         </is>
       </c>
       <c r="D18" s="2" t="inlineStr">
         <is>
-          <t>19058; 38672</t>
+          <t>19166; 39135</t>
         </is>
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>72803; 101200</t>
+          <t>72311; 101441</t>
         </is>
       </c>
       <c r="F18" s="2" t="inlineStr">
         <is>
-          <t>75145; 97410</t>
+          <t>74636; 98922</t>
         </is>
       </c>
       <c r="G18" s="2" t="inlineStr">
         <is>
-          <t>65960; 92904</t>
+          <t>66866; 94132</t>
         </is>
       </c>
       <c r="H18" s="2" t="inlineStr">
         <is>
-          <t>56429; 83976</t>
+          <t>55535; 83745</t>
         </is>
       </c>
       <c r="I18" s="2" t="inlineStr">
         <is>
-          <t>95606; 126177</t>
+          <t>96194; 124252</t>
         </is>
       </c>
       <c r="J18" s="2" t="inlineStr">
         <is>
-          <t>113919; 133832</t>
+          <t>113534; 133746</t>
         </is>
       </c>
       <c r="K18" s="2" t="inlineStr">
         <is>
-          <t>122524; 159431</t>
+          <t>121574; 160516</t>
         </is>
       </c>
       <c r="L18" s="2" t="inlineStr">
         <is>
-          <t>80737; 115657</t>
+          <t>79635; 114563</t>
         </is>
       </c>
       <c r="M18" s="2" t="inlineStr">
         <is>
-          <t>179901; 218107</t>
+          <t>179193; 218075</t>
         </is>
       </c>
       <c r="N18" s="2" t="inlineStr">
         <is>
-          <t>195345; 226101</t>
+          <t>195631; 227285</t>
         </is>
       </c>
     </row>
@@ -3249,62 +3249,62 @@
       </c>
       <c r="C21" s="2" t="inlineStr">
         <is>
-          <t>8431; 23279</t>
+          <t>7796; 22614</t>
         </is>
       </c>
       <c r="D21" s="2" t="inlineStr">
         <is>
-          <t>33736; 58820</t>
+          <t>33278; 58157</t>
         </is>
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>22247; 43801</t>
+          <t>22610; 43871</t>
         </is>
       </c>
       <c r="F21" s="2" t="inlineStr">
         <is>
-          <t>34523; 55644</t>
+          <t>33759; 55004</t>
         </is>
       </c>
       <c r="G21" s="2" t="inlineStr">
         <is>
-          <t>30570; 55780</t>
+          <t>31451; 55203</t>
         </is>
       </c>
       <c r="H21" s="2" t="inlineStr">
         <is>
-          <t>58021; 87418</t>
+          <t>58842; 88160</t>
         </is>
       </c>
       <c r="I21" s="2" t="inlineStr">
         <is>
-          <t>50142; 77070</t>
+          <t>51081; 79907</t>
         </is>
       </c>
       <c r="J21" s="2" t="inlineStr">
         <is>
-          <t>42509; 61864</t>
+          <t>42620; 60719</t>
         </is>
       </c>
       <c r="K21" s="2" t="inlineStr">
         <is>
-          <t>41306; 69838</t>
+          <t>40954; 70217</t>
         </is>
       </c>
       <c r="L21" s="2" t="inlineStr">
         <is>
-          <t>96987; 135858</t>
+          <t>98248; 137515</t>
         </is>
       </c>
       <c r="M21" s="2" t="inlineStr">
         <is>
-          <t>77710; 114905</t>
+          <t>77948; 115644</t>
         </is>
       </c>
       <c r="N21" s="2" t="inlineStr">
         <is>
-          <t>81172; 109131</t>
+          <t>81400; 108440</t>
         </is>
       </c>
     </row>
@@ -3457,62 +3457,62 @@
       </c>
       <c r="C24" s="2" t="inlineStr">
         <is>
-          <t>70028; 106005</t>
+          <t>70030; 105986</t>
         </is>
       </c>
       <c r="D24" s="2" t="inlineStr">
         <is>
-          <t>106753; 149551</t>
+          <t>106686; 146939</t>
         </is>
       </c>
       <c r="E24" s="2" t="inlineStr">
         <is>
-          <t>114205; 158380</t>
+          <t>113113; 158318</t>
         </is>
       </c>
       <c r="F24" s="2" t="inlineStr">
         <is>
-          <t>144270; 199369</t>
+          <t>140352; 196885</t>
         </is>
       </c>
       <c r="G24" s="2" t="inlineStr">
         <is>
-          <t>108451; 148762</t>
+          <t>110700; 150906</t>
         </is>
       </c>
       <c r="H24" s="2" t="inlineStr">
         <is>
-          <t>141355; 189705</t>
+          <t>143663; 188990</t>
         </is>
       </c>
       <c r="I24" s="2" t="inlineStr">
         <is>
-          <t>182530; 233128</t>
+          <t>181851; 232911</t>
         </is>
       </c>
       <c r="J24" s="2" t="inlineStr">
         <is>
-          <t>300476; 687088</t>
+          <t>301065; 648220</t>
         </is>
       </c>
       <c r="K24" s="2" t="inlineStr">
         <is>
-          <t>190510; 241481</t>
+          <t>191912; 244502</t>
         </is>
       </c>
       <c r="L24" s="2" t="inlineStr">
         <is>
-          <t>258867; 323568</t>
+          <t>260116; 323322</t>
         </is>
       </c>
       <c r="M24" s="2" t="inlineStr">
         <is>
-          <t>310174; 377606</t>
+          <t>310807; 377088</t>
         </is>
       </c>
       <c r="N24" s="2" t="inlineStr">
         <is>
-          <t>455630; 959679</t>
+          <t>452348; 960874</t>
         </is>
       </c>
     </row>
@@ -3665,62 +3665,62 @@
       </c>
       <c r="C27" s="2" t="inlineStr">
         <is>
-          <t>195871; 244337</t>
+          <t>197051; 246654</t>
         </is>
       </c>
       <c r="D27" s="2" t="inlineStr">
         <is>
-          <t>232530; 287393</t>
+          <t>232205; 289793</t>
         </is>
       </c>
       <c r="E27" s="2" t="inlineStr">
         <is>
-          <t>125935; 169866</t>
+          <t>125735; 171825</t>
         </is>
       </c>
       <c r="F27" s="2" t="inlineStr">
         <is>
-          <t>68820; 217631</t>
+          <t>69477; 219439</t>
         </is>
       </c>
       <c r="G27" s="2" t="inlineStr">
         <is>
-          <t>254091; 309203</t>
+          <t>253670; 307727</t>
         </is>
       </c>
       <c r="H27" s="2" t="inlineStr">
         <is>
-          <t>293408; 351183</t>
+          <t>292264; 351389</t>
         </is>
       </c>
       <c r="I27" s="2" t="inlineStr">
         <is>
-          <t>162091; 212508</t>
+          <t>162917; 212956</t>
         </is>
       </c>
       <c r="J27" s="2" t="inlineStr">
         <is>
-          <t>196587; 236504</t>
+          <t>196295; 240093</t>
         </is>
       </c>
       <c r="K27" s="2" t="inlineStr">
         <is>
-          <t>464360; 540434</t>
+          <t>466592; 538355</t>
         </is>
       </c>
       <c r="L27" s="2" t="inlineStr">
         <is>
-          <t>548418; 625296</t>
+          <t>540319; 622646</t>
         </is>
       </c>
       <c r="M27" s="2" t="inlineStr">
         <is>
-          <t>303736; 372869</t>
+          <t>302549; 370057</t>
         </is>
       </c>
       <c r="N27" s="2" t="inlineStr">
         <is>
-          <t>225528; 448964</t>
+          <t>218500; 444381</t>
         </is>
       </c>
     </row>
@@ -3873,62 +3873,62 @@
       </c>
       <c r="C30" s="2" t="inlineStr">
         <is>
-          <t>567515; 656212</t>
+          <t>570263; 662516</t>
         </is>
       </c>
       <c r="D30" s="2" t="inlineStr">
         <is>
-          <t>713821; 814262</t>
+          <t>712305; 815399</t>
         </is>
       </c>
       <c r="E30" s="2" t="inlineStr">
         <is>
-          <t>593816; 685543</t>
+          <t>597445; 688115</t>
         </is>
       </c>
       <c r="F30" s="2" t="inlineStr">
         <is>
-          <t>485466; 699541</t>
+          <t>501790; 702537</t>
         </is>
       </c>
       <c r="G30" s="2" t="inlineStr">
         <is>
-          <t>841377; 950929</t>
+          <t>846053; 947894</t>
         </is>
       </c>
       <c r="H30" s="2" t="inlineStr">
         <is>
-          <t>1105945; 1228193</t>
+          <t>1102324; 1216963</t>
         </is>
       </c>
       <c r="I30" s="2" t="inlineStr">
         <is>
-          <t>898089; 1003188</t>
+          <t>897801; 1007196</t>
         </is>
       </c>
       <c r="J30" s="2" t="inlineStr">
         <is>
-          <t>953102; 1577346</t>
+          <t>954129; 1594929</t>
         </is>
       </c>
       <c r="K30" s="2" t="inlineStr">
         <is>
-          <t>1444252; 1579259</t>
+          <t>1446647; 1569483</t>
         </is>
       </c>
       <c r="L30" s="2" t="inlineStr">
         <is>
-          <t>1847857; 1995433</t>
+          <t>1850649; 2004043</t>
         </is>
       </c>
       <c r="M30" s="2" t="inlineStr">
         <is>
-          <t>1519999; 1660006</t>
+          <t>1521629; 1663316</t>
         </is>
       </c>
       <c r="N30" s="2" t="inlineStr">
         <is>
-          <t>1551484; 2271052</t>
+          <t>1545530; 2324808</t>
         </is>
       </c>
     </row>

--- a/data/trans_dic/MCS12_SP_R3-Provincia-trans_dic.xlsx
+++ b/data/trans_dic/MCS12_SP_R3-Provincia-trans_dic.xlsx
@@ -664,7 +664,7 @@
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>6,61%</t>
+          <t>6,02%</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -684,7 +684,7 @@
       </c>
       <c r="J4" s="2" t="inlineStr">
         <is>
-          <t>7,26%</t>
+          <t>6,82%</t>
         </is>
       </c>
       <c r="K4" s="2" t="inlineStr">
@@ -704,7 +704,7 @@
       </c>
       <c r="N4" s="2" t="inlineStr">
         <is>
-          <t>6,92%</t>
+          <t>6,41%</t>
         </is>
       </c>
     </row>
@@ -717,62 +717,62 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>13,3; 23,22</t>
+          <t>12,77; 22,21</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>27,12; 38,3</t>
+          <t>27,6; 38,53</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>26,3; 37,14</t>
+          <t>26,07; 37,41</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>4,26; 10,09</t>
+          <t>3,86; 8,75</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>20,2; 31,43</t>
+          <t>20,14; 31,83</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>46,58; 59,17</t>
+          <t>46,52; 59,0</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>37,9; 49,64</t>
+          <t>37,56; 49,7</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
         <is>
-          <t>5,18; 9,79</t>
+          <t>4,94; 9,21</t>
         </is>
       </c>
       <c r="K5" s="2" t="inlineStr">
         <is>
-          <t>17,75; 25,44</t>
+          <t>17,8; 25,34</t>
         </is>
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>38,62; 46,9</t>
+          <t>38,88; 47,26</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>33,07; 41,2</t>
+          <t>33,66; 41,66</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
         <is>
-          <t>5,27; 8,87</t>
+          <t>4,98; 8,13</t>
         </is>
       </c>
     </row>
@@ -804,7 +804,7 @@
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>15,61%</t>
+          <t>15,87%</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
@@ -824,7 +824,7 @@
       </c>
       <c r="J6" s="2" t="inlineStr">
         <is>
-          <t>24,18%</t>
+          <t>24,22%</t>
         </is>
       </c>
       <c r="K6" s="2" t="inlineStr">
@@ -844,7 +844,7 @@
       </c>
       <c r="N6" s="2" t="inlineStr">
         <is>
-          <t>19,88%</t>
+          <t>20,11%</t>
         </is>
       </c>
     </row>
@@ -857,62 +857,62 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>22,63; 30,84</t>
+          <t>22,24; 30,46</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>11,89; 18,64</t>
+          <t>12,08; 18,71</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>6,33; 11,11</t>
+          <t>6,37; 11,24</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>12,02; 19,45</t>
+          <t>12,59; 20,0</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>36,6; 45,42</t>
+          <t>37,16; 45,29</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>21,71; 29,47</t>
+          <t>21,69; 30,18</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>12,54; 19,12</t>
+          <t>12,02; 18,65</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
         <is>
-          <t>21,2; 27,95</t>
+          <t>21,35; 27,69</t>
         </is>
       </c>
       <c r="K7" s="2" t="inlineStr">
         <is>
-          <t>30,95; 36,91</t>
+          <t>30,6; 36,52</t>
         </is>
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>18,0; 23,35</t>
+          <t>18,09; 23,22</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>10,03; 14,09</t>
+          <t>10,09; 14,05</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
         <is>
-          <t>17,36; 22,51</t>
+          <t>17,56; 22,85</t>
         </is>
       </c>
     </row>
@@ -944,7 +944,7 @@
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>13,06%</t>
+          <t>13,97%</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -964,7 +964,7 @@
       </c>
       <c r="J8" s="2" t="inlineStr">
         <is>
-          <t>19,8%</t>
+          <t>20,12%</t>
         </is>
       </c>
       <c r="K8" s="2" t="inlineStr">
@@ -984,7 +984,7 @@
       </c>
       <c r="N8" s="2" t="inlineStr">
         <is>
-          <t>16,58%</t>
+          <t>17,22%</t>
         </is>
       </c>
     </row>
@@ -997,62 +997,62 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>1,92; 6,58</t>
+          <t>1,79; 6,15</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>11,2; 19,11</t>
+          <t>11,47; 19,51</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>7,0; 13,46</t>
+          <t>6,71; 13,2</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>9,96; 16,95</t>
+          <t>10,51; 17,98</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>7,14; 14,2</t>
+          <t>7,24; 13,58</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>19,17; 28,19</t>
+          <t>19,33; 28,63</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>11,39; 18,73</t>
+          <t>11,2; 19,01</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>16,41; 23,35</t>
+          <t>16,76; 23,83</t>
         </is>
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>5,22; 9,11</t>
+          <t>5,17; 9,13</t>
         </is>
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>16,39; 22,26</t>
+          <t>16,71; 22,68</t>
         </is>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>10,07; 14,89</t>
+          <t>10,26; 15,18</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
         <is>
-          <t>14,24; 19,27</t>
+          <t>14,85; 19,91</t>
         </is>
       </c>
     </row>
@@ -1084,7 +1084,7 @@
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>12,43%</t>
+          <t>13,06%</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -1104,7 +1104,7 @@
       </c>
       <c r="J10" s="2" t="inlineStr">
         <is>
-          <t>17,23%</t>
+          <t>21,69%</t>
         </is>
       </c>
       <c r="K10" s="2" t="inlineStr">
@@ -1124,7 +1124,7 @@
       </c>
       <c r="N10" s="2" t="inlineStr">
         <is>
-          <t>15,34%</t>
+          <t>17,65%</t>
         </is>
       </c>
     </row>
@@ -1137,62 +1137,62 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>6,87; 13,4</t>
+          <t>7,08; 13,38</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>18,3; 27,13</t>
+          <t>17,74; 26,75</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>15,64; 23,48</t>
+          <t>15,68; 23,69</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>8,81; 16,9</t>
+          <t>9,65; 17,63</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>12,88; 20,29</t>
+          <t>12,71; 20,44</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>37,6; 47,26</t>
+          <t>37,17; 47,57</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>27,37; 37,68</t>
+          <t>27,54; 37,24</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
         <is>
-          <t>10,44; 22,56</t>
+          <t>17,97; 26,4</t>
         </is>
       </c>
       <c r="K11" s="2" t="inlineStr">
         <is>
-          <t>10,76; 15,74</t>
+          <t>10,78; 15,72</t>
         </is>
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>28,94; 35,79</t>
+          <t>29,08; 36,0</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>22,65; 29,53</t>
+          <t>22,65; 29,51</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
         <is>
-          <t>11,1; 18,74</t>
+          <t>14,97; 20,76</t>
         </is>
       </c>
     </row>
@@ -1224,7 +1224,7 @@
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>48,43%</t>
+          <t>47,62%</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
@@ -1244,7 +1244,7 @@
       </c>
       <c r="J12" s="2" t="inlineStr">
         <is>
-          <t>59,99%</t>
+          <t>58,97%</t>
         </is>
       </c>
       <c r="K12" s="2" t="inlineStr">
@@ -1264,7 +1264,7 @@
       </c>
       <c r="N12" s="2" t="inlineStr">
         <is>
-          <t>54,64%</t>
+          <t>53,56%</t>
         </is>
       </c>
     </row>
@@ -1277,62 +1277,62 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t>24,52; 37,44</t>
+          <t>24,84; 37,53</t>
         </is>
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>9,01; 18,41</t>
+          <t>8,72; 18,05</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>34,23; 48,03</t>
+          <t>34,98; 47,71</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>41,87; 55,5</t>
+          <t>41,17; 53,82</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
         <is>
-          <t>32,2; 45,33</t>
+          <t>31,45; 44,83</t>
         </is>
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>25,29; 38,14</t>
+          <t>25,79; 38,13</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>44,01; 56,84</t>
+          <t>44,59; 57,32</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
         <is>
-          <t>54,94; 64,72</t>
+          <t>53,85; 63,78</t>
         </is>
       </c>
       <c r="K13" s="2" t="inlineStr">
         <is>
-          <t>29,58; 39,06</t>
+          <t>29,92; 39,22</t>
         </is>
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>18,43; 26,51</t>
+          <t>18,63; 26,47</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>41,69; 50,74</t>
+          <t>40,73; 50,31</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
         <is>
-          <t>50,83; 59,05</t>
+          <t>49,36; 57,41</t>
         </is>
       </c>
     </row>
@@ -1364,7 +1364,7 @@
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>16,12%</t>
+          <t>15,53%</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -1384,7 +1384,7 @@
       </c>
       <c r="J14" s="2" t="inlineStr">
         <is>
-          <t>19,92%</t>
+          <t>19,99%</t>
         </is>
       </c>
       <c r="K14" s="2" t="inlineStr">
@@ -1404,7 +1404,7 @@
       </c>
       <c r="N14" s="2" t="inlineStr">
         <is>
-          <t>17,98%</t>
+          <t>17,73%</t>
         </is>
       </c>
     </row>
@@ -1417,62 +1417,62 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>2,88; 8,35</t>
+          <t>3,18; 8,61</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>12,15; 21,23</t>
+          <t>12,36; 21,43</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>8,59; 16,67</t>
+          <t>8,47; 16,39</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>12,54; 20,44</t>
+          <t>12,31; 19,38</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
         <is>
-          <t>11,31; 19,85</t>
+          <t>10,94; 19,69</t>
         </is>
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
-          <t>21,01; 31,48</t>
+          <t>20,63; 31,52</t>
         </is>
       </c>
       <c r="I15" s="2" t="inlineStr">
         <is>
-          <t>18,7; 29,26</t>
+          <t>18,43; 28,91</t>
         </is>
       </c>
       <c r="J15" s="2" t="inlineStr">
         <is>
-          <t>16,58; 23,62</t>
+          <t>16,35; 23,84</t>
         </is>
       </c>
       <c r="K15" s="2" t="inlineStr">
         <is>
-          <t>7,46; 12,79</t>
+          <t>7,72; 12,95</t>
         </is>
       </c>
       <c r="L15" s="2" t="inlineStr">
         <is>
-          <t>17,73; 24,82</t>
+          <t>17,92; 25,09</t>
         </is>
       </c>
       <c r="M15" s="2" t="inlineStr">
         <is>
-          <t>14,54; 21,57</t>
+          <t>14,58; 21,67</t>
         </is>
       </c>
       <c r="N15" s="2" t="inlineStr">
         <is>
-          <t>15,47; 20,61</t>
+          <t>15,24; 20,61</t>
         </is>
       </c>
     </row>
@@ -1504,7 +1504,7 @@
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>27,04%</t>
+          <t>25,38%</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -1524,7 +1524,7 @@
       </c>
       <c r="J16" s="2" t="inlineStr">
         <is>
-          <t>52,01%</t>
+          <t>37,17%</t>
         </is>
       </c>
       <c r="K16" s="2" t="inlineStr">
@@ -1544,7 +1544,7 @@
       </c>
       <c r="N16" s="2" t="inlineStr">
         <is>
-          <t>41,46%</t>
+          <t>31,49%</t>
         </is>
       </c>
     </row>
@@ -1557,62 +1557,62 @@
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
-          <t>11,39; 17,23</t>
+          <t>11,7; 17,32</t>
         </is>
       </c>
       <c r="D17" s="2" t="inlineStr">
         <is>
-          <t>16,1; 22,17</t>
+          <t>15,92; 22,16</t>
         </is>
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>17,23; 24,11</t>
+          <t>17,4; 24,07</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>22,64; 31,76</t>
+          <t>21,78; 29,38</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
         <is>
-          <t>17,35; 23,64</t>
+          <t>17,03; 23,26</t>
         </is>
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>20,71; 27,24</t>
+          <t>20,36; 27,09</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>26,31; 33,69</t>
+          <t>26,08; 33,42</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
         <is>
-          <t>35,55; 76,54</t>
+          <t>34,08; 40,48</t>
         </is>
       </c>
       <c r="K17" s="2" t="inlineStr">
         <is>
-          <t>15,31; 19,51</t>
+          <t>15,02; 19,32</t>
         </is>
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>19,17; 23,83</t>
+          <t>19,18; 23,95</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>23,06; 27,98</t>
+          <t>22,96; 27,94</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
         <is>
-          <t>30,84; 65,51</t>
+          <t>29,06; 33,88</t>
         </is>
       </c>
     </row>
@@ -1644,7 +1644,7 @@
       </c>
       <c r="F18" s="2" t="inlineStr">
         <is>
-          <t>16,66%</t>
+          <t>21,98%</t>
         </is>
       </c>
       <c r="G18" s="2" t="inlineStr">
@@ -1664,7 +1664,7 @@
       </c>
       <c r="J18" s="2" t="inlineStr">
         <is>
-          <t>30,23%</t>
+          <t>29,66%</t>
         </is>
       </c>
       <c r="K18" s="2" t="inlineStr">
@@ -1684,7 +1684,7 @@
       </c>
       <c r="N18" s="2" t="inlineStr">
         <is>
-          <t>22,57%</t>
+          <t>25,9%</t>
         </is>
       </c>
     </row>
@@ -1697,62 +1697,62 @@
       </c>
       <c r="C19" s="2" t="inlineStr">
         <is>
-          <t>26,49; 33,16</t>
+          <t>26,27; 33,14</t>
         </is>
       </c>
       <c r="D19" s="2" t="inlineStr">
         <is>
-          <t>29,8; 37,2</t>
+          <t>29,83; 36,92</t>
         </is>
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>16,15; 22,07</t>
+          <t>16,31; 21,89</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>7,49; 23,67</t>
+          <t>19,03; 24,74</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
         <is>
-          <t>32,38; 39,28</t>
+          <t>32,14; 38,94</t>
         </is>
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>35,48; 42,65</t>
+          <t>35,62; 42,49</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>19,72; 25,78</t>
+          <t>19,58; 25,64</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
         <is>
-          <t>27,44; 33,57</t>
+          <t>26,99; 32,5</t>
         </is>
       </c>
       <c r="K19" s="2" t="inlineStr">
         <is>
-          <t>30,55; 35,25</t>
+          <t>30,47; 35,21</t>
         </is>
       </c>
       <c r="L19" s="2" t="inlineStr">
         <is>
-          <t>33,71; 38,84</t>
+          <t>34,06; 38,73</t>
         </is>
       </c>
       <c r="M19" s="2" t="inlineStr">
         <is>
-          <t>18,85; 23,06</t>
+          <t>18,74; 23,04</t>
         </is>
       </c>
       <c r="N19" s="2" t="inlineStr">
         <is>
-          <t>13,3; 27,06</t>
+          <t>23,9; 27,94</t>
         </is>
       </c>
     </row>
@@ -1784,7 +1784,7 @@
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>18,36%</t>
+          <t>19,66%</t>
         </is>
       </c>
       <c r="G20" s="2" t="inlineStr">
@@ -1804,7 +1804,7 @@
       </c>
       <c r="J20" s="2" t="inlineStr">
         <is>
-          <t>30,91%</t>
+          <t>27,77%</t>
         </is>
       </c>
       <c r="K20" s="2" t="inlineStr">
@@ -1824,7 +1824,7 @@
       </c>
       <c r="N20" s="2" t="inlineStr">
         <is>
-          <t>24,81%</t>
+          <t>23,83%</t>
         </is>
       </c>
     </row>
@@ -1837,62 +1837,62 @@
       </c>
       <c r="C21" s="2" t="inlineStr">
         <is>
-          <t>17,4; 20,22</t>
+          <t>17,28; 19,96</t>
         </is>
       </c>
       <c r="D21" s="2" t="inlineStr">
         <is>
-          <t>20,79; 23,79</t>
+          <t>20,95; 23,86</t>
         </is>
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>17,6; 20,27</t>
+          <t>17,61; 20,22</t>
         </is>
       </c>
       <c r="F21" s="2" t="inlineStr">
         <is>
-          <t>14,57; 20,4</t>
+          <t>18,1; 21,1</t>
         </is>
       </c>
       <c r="G21" s="2" t="inlineStr">
         <is>
-          <t>25,04; 28,05</t>
+          <t>25,04; 27,96</t>
         </is>
       </c>
       <c r="H21" s="2" t="inlineStr">
         <is>
-          <t>30,98; 34,2</t>
+          <t>31,04; 34,38</t>
         </is>
       </c>
       <c r="I21" s="2" t="inlineStr">
         <is>
-          <t>25,33; 28,42</t>
+          <t>25,3; 28,41</t>
         </is>
       </c>
       <c r="J21" s="2" t="inlineStr">
         <is>
-          <t>26,19; 43,77</t>
+          <t>26,5; 28,97</t>
         </is>
       </c>
       <c r="K21" s="2" t="inlineStr">
         <is>
-          <t>21,74; 23,58</t>
+          <t>21,66; 23,63</t>
         </is>
       </c>
       <c r="L21" s="2" t="inlineStr">
         <is>
-          <t>26,49; 28,69</t>
+          <t>26,52; 28,64</t>
         </is>
       </c>
       <c r="M21" s="2" t="inlineStr">
         <is>
-          <t>21,93; 23,97</t>
+          <t>21,93; 24,0</t>
         </is>
       </c>
       <c r="N21" s="2" t="inlineStr">
         <is>
-          <t>21,81; 32,8</t>
+          <t>22,94; 24,79</t>
         </is>
       </c>
     </row>
@@ -2156,7 +2156,7 @@
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>20587</t>
+          <t>19181</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -2176,7 +2176,7 @@
       </c>
       <c r="J5" s="2" t="inlineStr">
         <is>
-          <t>21029</t>
+          <t>21544</t>
         </is>
       </c>
       <c r="K5" s="2" t="inlineStr">
@@ -2196,7 +2196,7 @@
       </c>
       <c r="N5" s="2" t="inlineStr">
         <is>
-          <t>41616</t>
+          <t>40726</t>
         </is>
       </c>
     </row>
@@ -2209,62 +2209,62 @@
       </c>
       <c r="C6" s="2" t="inlineStr">
         <is>
-          <t>36303; 63398</t>
+          <t>34875; 60638</t>
         </is>
       </c>
       <c r="D6" s="2" t="inlineStr">
         <is>
-          <t>79934; 112898</t>
+          <t>81341; 113569</t>
         </is>
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>77257; 109096</t>
+          <t>76572; 109909</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>13262; 31424</t>
+          <t>12308; 27904</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
         <is>
-          <t>52683; 81990</t>
+          <t>52536; 83027</t>
         </is>
       </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t>133790; 169955</t>
+          <t>133622; 169482</t>
         </is>
       </c>
       <c r="I6" s="2" t="inlineStr">
         <is>
-          <t>109421; 143319</t>
+          <t>108446; 143482</t>
         </is>
       </c>
       <c r="J6" s="2" t="inlineStr">
         <is>
-          <t>14996; 28351</t>
+          <t>15603; 29105</t>
         </is>
       </c>
       <c r="K6" s="2" t="inlineStr">
         <is>
-          <t>94771; 135794</t>
+          <t>95025; 135275</t>
         </is>
       </c>
       <c r="L6" s="2" t="inlineStr">
         <is>
-          <t>224754; 272928</t>
+          <t>226267; 275044</t>
         </is>
       </c>
       <c r="M6" s="2" t="inlineStr">
         <is>
-          <t>192628; 239974</t>
+          <t>196038; 242675</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
         <is>
-          <t>31695; 53301</t>
+          <t>31607; 51648</t>
         </is>
       </c>
     </row>
@@ -2364,7 +2364,7 @@
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>80791</t>
+          <t>84057</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -2384,7 +2384,7 @@
       </c>
       <c r="J8" s="2" t="inlineStr">
         <is>
-          <t>124163</t>
+          <t>132010</t>
         </is>
       </c>
       <c r="K8" s="2" t="inlineStr">
@@ -2404,7 +2404,7 @@
       </c>
       <c r="N8" s="2" t="inlineStr">
         <is>
-          <t>204953</t>
+          <t>216067</t>
         </is>
       </c>
     </row>
@@ -2417,62 +2417,62 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>111561; 152040</t>
+          <t>109672; 150174</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>60085; 94249</t>
+          <t>61063; 94575</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>31819; 55838</t>
+          <t>32028; 56495</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>62230; 100646</t>
+          <t>66690; 105950</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>184458; 228889</t>
+          <t>187280; 228255</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>113731; 154365</t>
+          <t>113629; 158064</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>65582; 100000</t>
+          <t>62856; 97553</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>108890; 143553</t>
+          <t>116384; 150905</t>
         </is>
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>308599; 367989</t>
+          <t>305074; 364120</t>
         </is>
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>185250; 240382</t>
+          <t>186168; 239009</t>
         </is>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>102859; 144465</t>
+          <t>103521; 144121</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
         <is>
-          <t>178970; 232149</t>
+          <t>188670; 245569</t>
         </is>
       </c>
     </row>
@@ -2572,7 +2572,7 @@
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>41010</t>
+          <t>43866</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -2592,7 +2592,7 @@
       </c>
       <c r="J11" s="2" t="inlineStr">
         <is>
-          <t>68147</t>
+          <t>70716</t>
         </is>
       </c>
       <c r="K11" s="2" t="inlineStr">
@@ -2612,7 +2612,7 @@
       </c>
       <c r="N11" s="2" t="inlineStr">
         <is>
-          <t>109157</t>
+          <t>114583</t>
         </is>
       </c>
     </row>
@@ -2625,62 +2625,62 @@
       </c>
       <c r="C12" s="2" t="inlineStr">
         <is>
-          <t>6113; 20969</t>
+          <t>5704; 19615</t>
         </is>
       </c>
       <c r="D12" s="2" t="inlineStr">
         <is>
-          <t>36289; 61924</t>
+          <t>37177; 63207</t>
         </is>
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>22299; 42895</t>
+          <t>21368; 42059</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>31287; 53242</t>
+          <t>33009; 56463</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
         <is>
-          <t>23939; 47641</t>
+          <t>24295; 45540</t>
         </is>
       </c>
       <c r="H12" s="2" t="inlineStr">
         <is>
-          <t>65361; 96149</t>
+          <t>65936; 97632</t>
         </is>
       </c>
       <c r="I12" s="2" t="inlineStr">
         <is>
-          <t>38311; 63005</t>
+          <t>37650; 63941</t>
         </is>
       </c>
       <c r="J12" s="2" t="inlineStr">
         <is>
-          <t>56455; 80364</t>
+          <t>58886; 83749</t>
         </is>
       </c>
       <c r="K12" s="2" t="inlineStr">
         <is>
-          <t>34123; 59618</t>
+          <t>33798; 59705</t>
         </is>
       </c>
       <c r="L12" s="2" t="inlineStr">
         <is>
-          <t>109011; 148034</t>
+          <t>111127; 150856</t>
         </is>
       </c>
       <c r="M12" s="2" t="inlineStr">
         <is>
-          <t>65950; 97523</t>
+          <t>67158; 99389</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
         <is>
-          <t>93694; 126847</t>
+          <t>98834; 132472</t>
         </is>
       </c>
     </row>
@@ -2780,7 +2780,7 @@
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>38063</t>
+          <t>47820</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -2800,7 +2800,7 @@
       </c>
       <c r="J14" s="2" t="inlineStr">
         <is>
-          <t>81065</t>
+          <t>90340</t>
         </is>
       </c>
       <c r="K14" s="2" t="inlineStr">
@@ -2820,7 +2820,7 @@
       </c>
       <c r="N14" s="2" t="inlineStr">
         <is>
-          <t>119129</t>
+          <t>138160</t>
         </is>
       </c>
     </row>
@@ -2833,62 +2833,62 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>24631; 48044</t>
+          <t>25407; 47995</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>68443; 101456</t>
+          <t>66344; 100027</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>57857; 86883</t>
+          <t>58002; 87659</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>26987; 51757</t>
+          <t>35324; 64564</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
         <is>
-          <t>47843; 75369</t>
+          <t>47210; 75908</t>
         </is>
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
-          <t>146253; 183828</t>
+          <t>144590; 185032</t>
         </is>
       </c>
       <c r="I15" s="2" t="inlineStr">
         <is>
-          <t>105987; 145941</t>
+          <t>106649; 144241</t>
         </is>
       </c>
       <c r="J15" s="2" t="inlineStr">
         <is>
-          <t>49130; 106157</t>
+          <t>74814; 109946</t>
         </is>
       </c>
       <c r="K15" s="2" t="inlineStr">
         <is>
-          <t>78551; 114897</t>
+          <t>78717; 114792</t>
         </is>
       </c>
       <c r="L15" s="2" t="inlineStr">
         <is>
-          <t>220787; 273079</t>
+          <t>221836; 274625</t>
         </is>
       </c>
       <c r="M15" s="2" t="inlineStr">
         <is>
-          <t>171482; 223621</t>
+          <t>171501; 223467</t>
         </is>
       </c>
       <c r="N15" s="2" t="inlineStr">
         <is>
-          <t>86228; 145521</t>
+          <t>117143; 162478</t>
         </is>
       </c>
     </row>
@@ -2988,7 +2988,7 @@
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>86316</t>
+          <t>97709</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -3008,7 +3008,7 @@
       </c>
       <c r="J17" s="2" t="inlineStr">
         <is>
-          <t>123969</t>
+          <t>132765</t>
         </is>
       </c>
       <c r="K17" s="2" t="inlineStr">
@@ -3028,7 +3028,7 @@
       </c>
       <c r="N17" s="2" t="inlineStr">
         <is>
-          <t>210285</t>
+          <t>230473</t>
         </is>
       </c>
     </row>
@@ -3041,62 +3041,62 @@
       </c>
       <c r="C18" s="2" t="inlineStr">
         <is>
-          <t>49847; 76126</t>
+          <t>50497; 76305</t>
         </is>
       </c>
       <c r="D18" s="2" t="inlineStr">
         <is>
-          <t>19166; 39135</t>
+          <t>18545; 38385</t>
         </is>
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>72311; 101441</t>
+          <t>73893; 100775</t>
         </is>
       </c>
       <c r="F18" s="2" t="inlineStr">
         <is>
-          <t>74636; 98922</t>
+          <t>84460; 110432</t>
         </is>
       </c>
       <c r="G18" s="2" t="inlineStr">
         <is>
-          <t>66866; 94132</t>
+          <t>65319; 93102</t>
         </is>
       </c>
       <c r="H18" s="2" t="inlineStr">
         <is>
-          <t>55535; 83745</t>
+          <t>56631; 83740</t>
         </is>
       </c>
       <c r="I18" s="2" t="inlineStr">
         <is>
-          <t>96194; 124252</t>
+          <t>97465; 125286</t>
         </is>
       </c>
       <c r="J18" s="2" t="inlineStr">
         <is>
-          <t>113534; 133746</t>
+          <t>121234; 143586</t>
         </is>
       </c>
       <c r="K18" s="2" t="inlineStr">
         <is>
-          <t>121574; 160516</t>
+          <t>122984; 161172</t>
         </is>
       </c>
       <c r="L18" s="2" t="inlineStr">
         <is>
-          <t>79635; 114563</t>
+          <t>80534; 114404</t>
         </is>
       </c>
       <c r="M18" s="2" t="inlineStr">
         <is>
-          <t>179193; 218075</t>
+          <t>175068; 216247</t>
         </is>
       </c>
       <c r="N18" s="2" t="inlineStr">
         <is>
-          <t>195631; 227285</t>
+          <t>212403; 247058</t>
         </is>
       </c>
     </row>
@@ -3196,7 +3196,7 @@
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>43392</t>
+          <t>41961</t>
         </is>
       </c>
       <c r="G20" s="2" t="inlineStr">
@@ -3216,7 +3216,7 @@
       </c>
       <c r="J20" s="2" t="inlineStr">
         <is>
-          <t>51215</t>
+          <t>52717</t>
         </is>
       </c>
       <c r="K20" s="2" t="inlineStr">
@@ -3236,7 +3236,7 @@
       </c>
       <c r="N20" s="2" t="inlineStr">
         <is>
-          <t>94607</t>
+          <t>94679</t>
         </is>
       </c>
     </row>
@@ -3249,62 +3249,62 @@
       </c>
       <c r="C21" s="2" t="inlineStr">
         <is>
-          <t>7796; 22614</t>
+          <t>8604; 23320</t>
         </is>
       </c>
       <c r="D21" s="2" t="inlineStr">
         <is>
-          <t>33278; 58157</t>
+          <t>33875; 58723</t>
         </is>
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>22610; 43871</t>
+          <t>22283; 43135</t>
         </is>
       </c>
       <c r="F21" s="2" t="inlineStr">
         <is>
-          <t>33759; 55004</t>
+          <t>33255; 52369</t>
         </is>
       </c>
       <c r="G21" s="2" t="inlineStr">
         <is>
-          <t>31451; 55203</t>
+          <t>30427; 54778</t>
         </is>
       </c>
       <c r="H21" s="2" t="inlineStr">
         <is>
-          <t>58842; 88160</t>
+          <t>57784; 88252</t>
         </is>
       </c>
       <c r="I21" s="2" t="inlineStr">
         <is>
-          <t>51081; 79907</t>
+          <t>50332; 78956</t>
         </is>
       </c>
       <c r="J21" s="2" t="inlineStr">
         <is>
-          <t>42620; 60719</t>
+          <t>43116; 62880</t>
         </is>
       </c>
       <c r="K21" s="2" t="inlineStr">
         <is>
-          <t>40954; 70217</t>
+          <t>42371; 71109</t>
         </is>
       </c>
       <c r="L21" s="2" t="inlineStr">
         <is>
-          <t>98248; 137515</t>
+          <t>99302; 138982</t>
         </is>
       </c>
       <c r="M21" s="2" t="inlineStr">
         <is>
-          <t>77948; 115644</t>
+          <t>78206; 116196</t>
         </is>
       </c>
       <c r="N21" s="2" t="inlineStr">
         <is>
-          <t>81400; 108440</t>
+          <t>81380; 110054</t>
         </is>
       </c>
     </row>
@@ -3404,7 +3404,7 @@
       </c>
       <c r="F23" s="2" t="inlineStr">
         <is>
-          <t>167644</t>
+          <t>181348</t>
         </is>
       </c>
       <c r="G23" s="2" t="inlineStr">
@@ -3424,7 +3424,7 @@
       </c>
       <c r="J23" s="2" t="inlineStr">
         <is>
-          <t>440416</t>
+          <t>285990</t>
         </is>
       </c>
       <c r="K23" s="2" t="inlineStr">
@@ -3444,7 +3444,7 @@
       </c>
       <c r="N23" s="2" t="inlineStr">
         <is>
-          <t>608060</t>
+          <t>467338</t>
         </is>
       </c>
     </row>
@@ -3457,62 +3457,62 @@
       </c>
       <c r="C24" s="2" t="inlineStr">
         <is>
-          <t>70030; 105986</t>
+          <t>71984; 106510</t>
         </is>
       </c>
       <c r="D24" s="2" t="inlineStr">
         <is>
-          <t>106686; 146939</t>
+          <t>105541; 146863</t>
         </is>
       </c>
       <c r="E24" s="2" t="inlineStr">
         <is>
-          <t>113113; 158318</t>
+          <t>114258; 158057</t>
         </is>
       </c>
       <c r="F24" s="2" t="inlineStr">
         <is>
-          <t>140352; 196885</t>
+          <t>155646; 209956</t>
         </is>
       </c>
       <c r="G24" s="2" t="inlineStr">
         <is>
-          <t>110700; 150906</t>
+          <t>108660; 148433</t>
         </is>
       </c>
       <c r="H24" s="2" t="inlineStr">
         <is>
-          <t>143663; 188990</t>
+          <t>141285; 187943</t>
         </is>
       </c>
       <c r="I24" s="2" t="inlineStr">
         <is>
-          <t>181851; 232911</t>
+          <t>180318; 231063</t>
         </is>
       </c>
       <c r="J24" s="2" t="inlineStr">
         <is>
-          <t>301065; 648220</t>
+          <t>262215; 311466</t>
         </is>
       </c>
       <c r="K24" s="2" t="inlineStr">
         <is>
-          <t>191912; 244502</t>
+          <t>188186; 242092</t>
         </is>
       </c>
       <c r="L24" s="2" t="inlineStr">
         <is>
-          <t>260116; 323322</t>
+          <t>260204; 324951</t>
         </is>
       </c>
       <c r="M24" s="2" t="inlineStr">
         <is>
-          <t>310807; 377088</t>
+          <t>309475; 376577</t>
         </is>
       </c>
       <c r="N24" s="2" t="inlineStr">
         <is>
-          <t>452348; 960874</t>
+          <t>431274; 502840</t>
         </is>
       </c>
     </row>
@@ -3612,7 +3612,7 @@
       </c>
       <c r="F26" s="2" t="inlineStr">
         <is>
-          <t>154440</t>
+          <t>175068</t>
         </is>
       </c>
       <c r="G26" s="2" t="inlineStr">
@@ -3632,7 +3632,7 @@
       </c>
       <c r="J26" s="2" t="inlineStr">
         <is>
-          <t>216219</t>
+          <t>245735</t>
         </is>
       </c>
       <c r="K26" s="2" t="inlineStr">
@@ -3652,7 +3652,7 @@
       </c>
       <c r="N26" s="2" t="inlineStr">
         <is>
-          <t>370659</t>
+          <t>420803</t>
         </is>
       </c>
     </row>
@@ -3665,62 +3665,62 @@
       </c>
       <c r="C27" s="2" t="inlineStr">
         <is>
-          <t>197051; 246654</t>
+          <t>195406; 246505</t>
         </is>
       </c>
       <c r="D27" s="2" t="inlineStr">
         <is>
-          <t>232205; 289793</t>
+          <t>232389; 287657</t>
         </is>
       </c>
       <c r="E27" s="2" t="inlineStr">
         <is>
-          <t>125735; 171825</t>
+          <t>126975; 170402</t>
         </is>
       </c>
       <c r="F27" s="2" t="inlineStr">
         <is>
-          <t>69477; 219439</t>
+          <t>151578; 196992</t>
         </is>
       </c>
       <c r="G27" s="2" t="inlineStr">
         <is>
-          <t>253670; 307727</t>
+          <t>251837; 305084</t>
         </is>
       </c>
       <c r="H27" s="2" t="inlineStr">
         <is>
-          <t>292264; 351389</t>
+          <t>293444; 350060</t>
         </is>
       </c>
       <c r="I27" s="2" t="inlineStr">
         <is>
-          <t>162917; 212956</t>
+          <t>161795; 211859</t>
         </is>
       </c>
       <c r="J27" s="2" t="inlineStr">
         <is>
-          <t>196295; 240093</t>
+          <t>223616; 269220</t>
         </is>
       </c>
       <c r="K27" s="2" t="inlineStr">
         <is>
-          <t>466592; 538355</t>
+          <t>465391; 537726</t>
         </is>
       </c>
       <c r="L27" s="2" t="inlineStr">
         <is>
-          <t>540319; 622646</t>
+          <t>545944; 620827</t>
         </is>
       </c>
       <c r="M27" s="2" t="inlineStr">
         <is>
-          <t>302549; 370057</t>
+          <t>300726; 369703</t>
         </is>
       </c>
       <c r="N27" s="2" t="inlineStr">
         <is>
-          <t>218500; 444381</t>
+          <t>388309; 454012</t>
         </is>
       </c>
     </row>
@@ -3820,7 +3820,7 @@
       </c>
       <c r="F29" s="2" t="inlineStr">
         <is>
-          <t>632243</t>
+          <t>691011</t>
         </is>
       </c>
       <c r="G29" s="2" t="inlineStr">
@@ -3840,7 +3840,7 @@
       </c>
       <c r="J29" s="2" t="inlineStr">
         <is>
-          <t>1126222</t>
+          <t>1031818</t>
         </is>
       </c>
       <c r="K29" s="2" t="inlineStr">
@@ -3860,7 +3860,7 @@
       </c>
       <c r="N29" s="2" t="inlineStr">
         <is>
-          <t>1758466</t>
+          <t>1722829</t>
         </is>
       </c>
     </row>
@@ -3873,62 +3873,62 @@
       </c>
       <c r="C30" s="2" t="inlineStr">
         <is>
-          <t>570263; 662516</t>
+          <t>566182; 653942</t>
         </is>
       </c>
       <c r="D30" s="2" t="inlineStr">
         <is>
-          <t>712305; 815399</t>
+          <t>718045; 817517</t>
         </is>
       </c>
       <c r="E30" s="2" t="inlineStr">
         <is>
-          <t>597445; 688115</t>
+          <t>597700; 686474</t>
         </is>
       </c>
       <c r="F30" s="2" t="inlineStr">
         <is>
-          <t>501790; 702537</t>
+          <t>636369; 741552</t>
         </is>
       </c>
       <c r="G30" s="2" t="inlineStr">
         <is>
-          <t>846053; 947894</t>
+          <t>846234; 944763</t>
         </is>
       </c>
       <c r="H30" s="2" t="inlineStr">
         <is>
-          <t>1102324; 1216963</t>
+          <t>1104449; 1223517</t>
         </is>
       </c>
       <c r="I30" s="2" t="inlineStr">
         <is>
-          <t>897801; 1007196</t>
+          <t>896862; 1007054</t>
         </is>
       </c>
       <c r="J30" s="2" t="inlineStr">
         <is>
-          <t>954129; 1594929</t>
+          <t>984640; 1076591</t>
         </is>
       </c>
       <c r="K30" s="2" t="inlineStr">
         <is>
-          <t>1446647; 1569483</t>
+          <t>1441934; 1573020</t>
         </is>
       </c>
       <c r="L30" s="2" t="inlineStr">
         <is>
-          <t>1850649; 2004043</t>
+          <t>1852183; 2000238</t>
         </is>
       </c>
       <c r="M30" s="2" t="inlineStr">
         <is>
-          <t>1521629; 1663316</t>
+          <t>1521531; 1665479</t>
         </is>
       </c>
       <c r="N30" s="2" t="inlineStr">
         <is>
-          <t>1545530; 2324808</t>
+          <t>1658876; 1792341</t>
         </is>
       </c>
     </row>
